--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-valueset-operationoutcome-details-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-valueset-operationoutcome-details-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-valueset-operationoutcome-details-vs.xlsx
+++ b/r4-ELGA-e-Medikation-main/ValueSet-at-elga-emed-valueset-operationoutcome-details-vs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>At ELGA e-Medikation ValueSet für AT e-Medikation OperationOutcome Details</t>
+    <t>AT ELGA e-Medikation ValueSet für OperationOutcome Details</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
